--- a/output/amkr_indicator_data.xlsx
+++ b/output/amkr_indicator_data.xlsx
@@ -20683,7 +20683,7 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -20814,10 +20814,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.2838943739527038</v>
+        <v>0.2561078137974995</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2520708549628556</v>
+        <v>0.2293399176269209</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>1511.392</v>
@@ -20826,10 +20826,10 @@
         <v>1750</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1892.36987362402</v>
+        <v>1858.014516781987</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>1967.657293615461</v>
+        <v>1933.301936773428</v>
       </c>
       <c r="L2" s="7" t="n">
         <v>1750</v>
@@ -20868,11 +20868,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>OSAT_COMPOSITE</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>3</v>
@@ -20881,22 +20881,22 @@
         <v>16</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.2838943739527038</v>
+        <v>0.3699436303194559</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.2607063253116539</v>
+        <v>0.1985206859207439</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1511.392</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1750</v>
+        <v>1722.477677696056</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1905.421454425432</v>
+        <v>1811.434576535125</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1983.765176311793</v>
+        <v>1900.391475374194</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>1750</v>
@@ -20916,10 +20916,10 @@
         <v/>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>0.7425769146357346</v>
+        <v>0.6681067953932439</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>0.0615901175968257</v>
+        <v>0.0699336938382162</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -20935,35 +20935,35 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OSAT_COMPOSITE</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2838943739527038</v>
+        <v>0.3405112657468818</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.2429187281651951</v>
+        <v>0.1965237697981598</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1511.392</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1750</v>
+        <v>1694.098334004944</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1878.537422399051</v>
+        <v>1808.41645348278</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1966.690350830798</v>
+        <v>1922.734572960617</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>1750</v>
@@ -20983,10 +20983,10 @@
         <v/>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>0.6931232616507226</v>
+        <v>0.4518880948617338</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>0.06930165044355729</v>
+        <v>0.0898714823926899</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>

--- a/output/amkr_indicator_data.xlsx
+++ b/output/amkr_indicator_data.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QTD" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lead_Lag" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment_Models" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix_Decomposition" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -554,97 +556,111 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Segment_Models  Advanced / Mainstream fits. Peer mapping is pre-specified, not searched.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Mix_Decomposition  How much of total YoY growth each product group contributed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan company revenue   TWD thousands (as filed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SIA billings             USD millions - NOTE: 3-month moving average, not discrete months</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Taiwan exports           USD millions</t>
+          <t>Taiwan company revenue   TWD thousands (as filed)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AMKR revenue             USD millions</t>
+          <t>SIA billings             USD millions - NOTE: 3-month moving average, not discrete months</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Taiwan exports           USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AMKR revenue             USD millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>OSAT_COMPOSITE           Index, first available month = 100, revenue-weighted</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Health warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>- All correlation work is in YoY space. Level correlations here are ~0.95+ and meaningless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>- 5 years of history is 20 quarters. Small sample; treat coefficients as indicative.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>- SIA data is smoothed and lags turning points. Confirmation, not a leading signal.</t>
+          <t>- All correlation work is in YoY space. Level correlations here are ~0.95+ and meaningless.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>- ASE monthly revenue includes USI's EMS business, which dilutes the pure OSAT read.</t>
+          <t>- 5 years of history is 20 quarters. Small sample; treat coefficients as indicative.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>- ChipMOS and PTI skew memory/display; AMKR skews advanced SiP, comms and auto.</t>
+          <t>- SIA data is smoothed and lags turning points. Confirmation, not a leading signal.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>- ASE monthly revenue includes USI's EMS business, which dilutes the pure OSAT read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>- ChipMOS and PTI skew memory/display; AMKR skews advanced SiP, comms and auto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Divergence between them is informative, not necessarily an error.</t>
         </is>
@@ -21004,4 +21020,900 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>peers</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>lead_months</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>n_obs</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>peer_yoy</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>implied_segment_yoy</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>prior_year_usdm</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>predicted_usdm</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>resid_sd_pp</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>in_sample_r2</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>corr_lead0</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>corr_lead1</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>corr_lead2</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>corr_lead3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AMKR_ADVANCED</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ASE+KYEC+TSMC</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.3424639450655884</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.1479492806355571</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1228.678</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>1410.460026232735</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0.1008013697573139</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.4280008765151527</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0.6542177592477545</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0.5992932695218303</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0.5973422461489907</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0.5061660360868826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AMKR_MAINSTREAM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PTI+CHIPMOS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.2826571062273382</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0001290798864365</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>282.714</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>282.750492691014</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.1356994568607963</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.0962030606948948</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.3101661823843712</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.3037022746837799</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.2433349733811644</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.2021160226731361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>total_yoy</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_ADVANCED_share</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_ADVANCED_yoy</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_ADVANCED_contrib</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_MAINSTREAM_share</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_MAINSTREAM_yoy</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>AMKR_MAINSTREAM_contrib</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>0.2491943571325112</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.7407333553418221</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.702907593700921</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.3819434513897282</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.2592666446581778</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.2907189125190427</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>-0.1327490942572171</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>0.1505566467930343</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.6942314217848659</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0.1583815334364229</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0.1092106998341164</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.305768578215134</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.133177210980357</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.0413459469589177</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0.1991851030216325</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6965116403075643</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1739946361420488</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1237896546108862</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.3034883596924356</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.2612968516849616</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.0753954484107462</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0.2414855582216843</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7351296847114812</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.2320936817651573</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.171919531647542</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.2648703152885187</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.2683184590361001</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.0695660265741424</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2021Q4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.25790840682372</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7381993037403661</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3096115390312546</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2195317280810712</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.2618006962596338</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.1319037245203649</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.0383766787426488</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.2040990838140481</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7242587749621747</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2561795678077021</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1778479055913735</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.2757412250378253</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0858530931330843</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.0262511782226746</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0.0699115201541376</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7201435607641336</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1062125128104622</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0739782515188032</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.2798564392358665</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-0.013399958300829</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>-0.0040667313646656</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.2395544318857825</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7867812453957904</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3266478009764089</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2401284949434861</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.2132187546042095</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.0021673363324178</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-0.0005740630577037</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2022Q4</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.1052773789837206</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7805808384175931</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1687336181429874</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1245590394307461</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.2194191615824069</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.07365014960809529</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.0192816604470255</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>-0.0784542489554213</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7253474083935254</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.0770690734521508</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.0558179527259246</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.2746525916064746</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.08209253522534229</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.0226362962294967</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-0.0311960916173378</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7437716146680001</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.0005905579018954</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.0004252864703083</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.2562283853319999</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.1129914257966933</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.0316213780876462</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-0.1256894616332268</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.7968561741097918</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1144936986438405</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.0900814948089711</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.2031438258902081</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.167002039245344</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-0.0356079668242555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-0.0809978963493005</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.815963594246183</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.0393406772131609</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.030708578802965</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.184036405753817</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-0.2291929163508735</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-0.0502893175463354</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>-0.0720524566457294</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7833763331089973</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.0021847950630378</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.0015847354368454</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.2166236668910027</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.2681103122015428</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-0.0736371920825747</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0.0024363443311783</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8072966060292553</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0880537016731513</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.0654918438709341</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1927033939707445</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2460909998634761</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.06305549953975589</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0.0218444137176945</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8420784609277344</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07983498047470999</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.0636169971012073</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.1579215390722657</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.2056305831617515</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.0417725833835128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-0.070037806589866</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8331520491456113</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.0504479458015661</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.0411636871785825</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.1668479508543886</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.1568935194806403</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.0288741194112835</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-0.0321755006001416</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.8048101696838998</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.00569500677287</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.0044613335227618</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.1951898303161001</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.1279369307847816</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-0.0277141670773798</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0.0341559275088025</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.8129446232347399</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.0413911003413165</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.0334148948253612</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.1870553767652601</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0038454573537716</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.0007410326834415</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0.06735052688858829</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.8472733330380762</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.0739351264732675</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.0622591775091064</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.1527266669619239</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0322397401227954</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.0050913493794817</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0.1589375355253577</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.8367142537840709</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.1638926606660413</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1365475060738386</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.163285746215929</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.1341942129757372</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.0223900294515191</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0.2747676068327562</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.8143884285698174</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.2899389535894969</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.2333458184363354</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.1856115714301825</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.2122128408500607</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.0414217883964209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/amkr_indicator_data.xlsx
+++ b/output/amkr_indicator_data.xlsx
@@ -20900,7 +20900,7 @@
         <v>0.3699436303194559</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1985206859207439</v>
+        <v>0.1985206859207438</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1511.392</v>
@@ -20912,7 +20912,7 @@
         <v>1811.434576535125</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1900.391475374194</v>
+        <v>1900.391475374193</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>1750</v>
@@ -20932,7 +20932,7 @@
         <v/>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>0.6681067953932439</v>
+        <v>0.668106795393244</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>0.0699336938382162</v>
@@ -21148,34 +21148,34 @@
         <v>17</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.3424639450655884</v>
+        <v>0.3343710507262332</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1479492806355571</v>
+        <v>0.1966516019501105</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>1228.678</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1410.460026232735</v>
+        <v>1470.299496980858</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.1008013697573139</v>
+        <v>0.0969582412221319</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.4280008765151527</v>
+        <v>0.4707852330787171</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.6542177592477545</v>
+        <v>0.6861379111218948</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.5992932695218303</v>
+        <v>0.7394411465751105</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.5973422461489907</v>
+        <v>0.7765947821841254</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.5061660360868826</v>
+        <v>0.7397210645127218</v>
       </c>
     </row>
     <row r="3">
@@ -21201,34 +21201,34 @@
         <v>17</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.2826571062273382</v>
+        <v>0.2833716042137224</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0001290798864365</v>
+        <v>-0.008086668819183501</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>282.714</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>282.750492691014</v>
+        <v>280.4277855114533</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.1356994568607963</v>
+        <v>0.1373714838838476</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0.0962030606948948</v>
+        <v>0.0737934957069088</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.3101661823843712</v>
+        <v>0.2716495825634729</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.3037022746837799</v>
+        <v>0.2644983610453707</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.2433349733811644</v>
+        <v>0.2101418405161259</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0.2021160226731361</v>
+        <v>0.1712509747106888</v>
       </c>
     </row>
   </sheetData>

--- a/output/amkr_indicator_data.xlsx
+++ b/output/amkr_indicator_data.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment_Models" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix_Decomposition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance_Record" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance_Current" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,6 +673,987 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>guide_low_usdm</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>guide_mid_usdm</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>guide_high_usdm</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>actual_usdm</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>position_in_range</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>vs_mid_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>above_mid</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>above_high</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>below_low</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1354.023</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1.540229999999999</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0832184</v>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2020Q4</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1371.041</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1.210409999999999</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.054646923076923</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1326.15</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.5615000000000009</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0046590909090908</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1406.535</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.165350000000001</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.049652985074627</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1681</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.0111764705882353</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2021Q4</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1690</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1724.644</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.34644</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0516121951219512</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1550</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1596.816</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.9681600000000004</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0302038709677419</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1470</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1570</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1504.868</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.3486799999999994</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.0099552631578947</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2083.691</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.036909999999998</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.0796326424870466</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2022Q4</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1906.21</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.0621</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.0303837837837837</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1471.539</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.7153899999999999</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.0148544827586207</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1475</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1525</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1457.922</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.3292200000000002</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.0115783050847457</v>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1725</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1821.793</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.967929999999999</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0263622535211267</v>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1675</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1725</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1751.811</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.268109999999999</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.0458573134328357</v>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1365.511</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6551099999999996</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.0114896296296296</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1461.474</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.6147399999999993</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.007913103448275701</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1785</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1861.589</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.7658899999999994</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0144899182561306</v>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1629.118</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.2911799999999994</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.0126557575757576</v>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1225</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1321.575</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.9657500000000004</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0365294117647059</v>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1475</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1511.392</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1.36392</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0606259649122806</v>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1875</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1925</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1986.968</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.119680000000001</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0321911688311689</v>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1775</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1875</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1888.046</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1.13046</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.0345457534246576</v>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1684.701</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.8470100000000003</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0210309090909091</v>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>guide_low_usdm</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>guide_mid_usdm</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>guide_high_usdm</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>peer_implied_usdm</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>peer_implied_sd_usdm</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>peer_implied_position_in_range</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>peer_vs_mid_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>bias_adjusted_guide_usdm</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>peer_vs_bias_adjusted_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>gap_vs_bias_adj_in_sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1858.014516781987</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>89.45535989097291</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1.080145167819872</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.0322302871011039</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>1846.793</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0.0060762179529525</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.1254426430754277</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -681,11 +1664,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -757,7 +1740,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -792,7 +1775,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -827,7 +1810,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -862,7 +1845,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -897,7 +1880,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -932,7 +1915,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -967,7 +1950,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1985,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1037,7 +2020,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1072,7 +2055,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1107,7 +2090,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1142,7 +2125,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1177,7 +2160,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1212,7 +2195,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1247,7 +2230,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1282,7 +2265,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1317,7 +2300,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1352,7 +2335,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1387,7 +2370,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1422,7 +2405,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1457,7 +2440,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1492,7 +2475,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1527,7 +2510,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1562,7 +2545,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1597,7 +2580,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1632,7 +2615,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1667,7 +2650,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1702,7 +2685,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1737,7 +2720,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1772,7 +2755,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1807,7 +2790,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1842,7 +2825,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1877,7 +2860,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2895,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1947,7 +2930,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2965,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2017,7 +3000,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2052,7 +3035,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2087,7 +3070,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2122,7 +3105,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2157,7 +3140,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2192,7 +3175,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2227,7 +3210,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2262,7 +3245,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2297,7 +3280,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2332,7 +3315,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2367,7 +3350,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2402,7 +3385,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2437,7 +3420,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2472,7 +3455,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2507,7 +3490,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2542,7 +3525,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2577,7 +3560,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2612,7 +3595,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2647,7 +3630,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2682,7 +3665,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2717,7 +3700,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2752,7 +3735,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2787,7 +3770,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2822,7 +3805,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2857,7 +3840,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2892,7 +3875,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2927,7 +3910,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3945,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3980,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3032,7 +4015,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3067,7 +4050,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3102,7 +4085,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3137,7 +4120,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3172,7 +4155,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3207,7 +4190,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3242,7 +4225,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3277,7 +4260,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3312,7 +4295,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3347,7 +4330,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3382,7 +4365,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3417,7 +4400,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3452,7 +4435,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3487,7 +4470,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3522,7 +4505,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3557,7 +4540,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3592,7 +4575,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3627,7 +4610,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3662,7 +4645,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3697,7 +4680,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3732,7 +4715,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3767,7 +4750,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3802,7 +4785,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3837,7 +4820,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3872,7 +4855,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3907,7 +4890,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3942,7 +4925,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3977,7 +4960,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4995,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4047,7 +5030,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4082,7 +5065,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4117,7 +5100,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4152,7 +5135,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4187,7 +5170,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4222,7 +5205,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4257,7 +5240,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4292,7 +5275,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4327,7 +5310,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4362,7 +5345,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4397,7 +5380,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4432,7 +5415,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4467,7 +5450,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4502,7 +5485,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4537,7 +5520,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4572,7 +5555,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4607,7 +5590,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4642,7 +5625,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4677,7 +5660,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4712,7 +5695,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4747,7 +5730,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4782,7 +5765,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4817,7 +5800,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4852,7 +5835,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4887,7 +5870,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4922,7 +5905,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4957,7 +5940,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5975,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5027,7 +6010,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5062,7 +6045,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5097,7 +6080,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5132,7 +6115,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5167,7 +6150,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5202,7 +6185,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5237,7 +6220,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5272,7 +6255,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5307,7 +6290,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5342,7 +6325,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5377,7 +6360,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5412,7 +6395,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5447,7 +6430,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5482,7 +6465,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5517,7 +6500,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5552,7 +6535,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5587,7 +6570,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5622,7 +6605,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5657,7 +6640,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5692,7 +6675,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5727,7 +6710,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5762,7 +6745,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5797,7 +6780,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5832,7 +6815,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5867,7 +6850,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5902,7 +6885,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5937,7 +6920,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -5972,7 +6955,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6990,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6042,7 +7025,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6077,7 +7060,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6112,7 +7095,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6147,7 +7130,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6182,7 +7165,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6217,7 +7200,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6252,7 +7235,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6287,7 +7270,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6322,7 +7305,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6357,7 +7340,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6392,7 +7375,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6427,7 +7410,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6462,7 +7445,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6497,7 +7480,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6532,7 +7515,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6567,7 +7550,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6602,7 +7585,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6637,7 +7620,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6672,7 +7655,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6707,7 +7690,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6742,7 +7725,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6777,7 +7760,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6812,7 +7795,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6847,7 +7830,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6882,7 +7865,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6917,7 +7900,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6952,7 +7935,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -6987,7 +7970,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7022,7 +8005,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7057,7 +8040,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7092,7 +8075,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7127,7 +8110,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7162,7 +8145,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7197,7 +8180,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7232,7 +8215,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7267,7 +8250,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7302,7 +8285,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7337,7 +8320,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7372,7 +8355,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7407,7 +8390,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7442,7 +8425,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7477,7 +8460,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7512,7 +8495,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7547,7 +8530,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7582,7 +8565,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7617,7 +8600,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7652,7 +8635,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7687,7 +8670,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7722,7 +8705,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7757,7 +8740,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7792,7 +8775,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7827,7 +8810,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7862,7 +8845,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7897,7 +8880,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7932,7 +8915,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -7967,7 +8950,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8985,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8037,7 +9020,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8072,7 +9055,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8107,7 +9090,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8142,7 +9125,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8177,7 +9160,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8212,7 +9195,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8247,7 +9230,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8282,7 +9265,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8317,7 +9300,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8352,7 +9335,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8387,7 +9370,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8422,7 +9405,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8457,7 +9440,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8492,7 +9475,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8527,7 +9510,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8562,7 +9545,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8597,7 +9580,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8632,7 +9615,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8667,7 +9650,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8702,7 +9685,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8737,7 +9720,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8772,7 +9755,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8807,7 +9790,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8842,7 +9825,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8877,7 +9860,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8912,7 +9895,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8947,7 +9930,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -8982,7 +9965,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9017,7 +10000,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9052,7 +10035,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9087,7 +10070,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9122,7 +10105,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9157,7 +10140,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9192,7 +10175,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9227,7 +10210,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9262,7 +10245,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9297,7 +10280,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9332,7 +10315,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9367,7 +10350,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9402,7 +10385,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9437,7 +10420,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9472,7 +10455,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9507,7 +10490,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9542,7 +10525,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9577,7 +10560,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9612,7 +10595,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9647,7 +10630,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9682,7 +10665,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9717,7 +10700,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9752,7 +10735,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9787,7 +10770,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9822,7 +10805,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9857,7 +10840,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9892,7 +10875,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9927,7 +10910,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9962,7 +10945,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -9997,7 +10980,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10032,7 +11015,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10067,7 +11050,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10102,7 +11085,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10137,7 +11120,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10172,7 +11155,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10207,7 +11190,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10242,7 +11225,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10277,7 +11260,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10312,7 +11295,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10347,7 +11330,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10382,7 +11365,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10417,7 +11400,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10452,7 +11435,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10487,7 +11470,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10522,7 +11505,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10557,7 +11540,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10592,7 +11575,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10627,7 +11610,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10662,7 +11645,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10697,7 +11680,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10732,7 +11715,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10767,7 +11750,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10802,7 +11785,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10837,7 +11820,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10872,7 +11855,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10907,7 +11890,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10942,7 +11925,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -10977,7 +11960,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11995,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11047,7 +12030,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11082,7 +12065,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11117,7 +12100,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11152,7 +12135,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11187,7 +12170,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11222,7 +12205,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11257,7 +12240,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11292,7 +12275,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11327,7 +12310,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11362,7 +12345,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11397,7 +12380,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11432,7 +12415,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11467,7 +12450,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11502,7 +12485,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11537,7 +12520,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11572,7 +12555,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11607,7 +12590,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11642,7 +12625,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11677,7 +12660,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11712,7 +12695,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11747,7 +12730,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11782,7 +12765,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11817,7 +12800,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11852,7 +12835,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11887,7 +12870,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11922,7 +12905,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11957,7 +12940,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11992,7 +12975,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12027,7 +13010,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12062,7 +13045,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12097,7 +13080,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12132,7 +13115,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12167,7 +13150,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12202,7 +13185,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12237,7 +13220,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12272,7 +13255,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12307,7 +13290,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12342,7 +13325,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12377,7 +13360,7 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12412,7 +13395,7 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12447,7 +13430,7 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12482,7 +13465,7 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12517,7 +13500,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12552,7 +13535,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12587,7 +13570,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12622,7 +13605,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12657,7 +13640,7 @@
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12692,7 +13675,7 @@
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12727,7 +13710,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12762,7 +13745,7 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12797,7 +13780,7 @@
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12832,7 +13815,7 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12867,7 +13850,7 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12902,7 +13885,7 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12937,7 +13920,7 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12972,7 +13955,7 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13990,7 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13042,7 +14025,7 @@
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13077,7 +14060,7 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13112,7 +14095,7 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13147,7 +14130,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13182,7 +14165,7 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13217,7 +14200,7 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13252,7 +14235,7 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13287,7 +14270,7 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13322,7 +14305,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13357,7 +14340,7 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13392,7 +14375,7 @@
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13427,7 +14410,7 @@
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13462,7 +14445,7 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13497,7 +14480,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13532,7 +14515,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13567,7 +14550,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13602,7 +14585,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13637,7 +14620,7 @@
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13672,7 +14655,7 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13707,7 +14690,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13742,7 +14725,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13777,7 +14760,7 @@
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13812,7 +14795,7 @@
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13847,7 +14830,7 @@
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13882,7 +14865,7 @@
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13917,7 +14900,7 @@
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13952,7 +14935,7 @@
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13987,7 +14970,7 @@
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14022,7 +15005,7 @@
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14057,7 +15040,7 @@
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14092,7 +15075,7 @@
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14127,7 +15110,7 @@
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14162,7 +15145,7 @@
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14197,7 +15180,7 @@
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14232,7 +15215,7 @@
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14267,7 +15250,7 @@
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14302,7 +15285,7 @@
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14337,7 +15320,7 @@
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14372,7 +15355,7 @@
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14407,7 +15390,7 @@
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14442,7 +15425,7 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14477,7 +15460,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14512,7 +15495,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14547,7 +15530,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14582,7 +15565,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14617,7 +15600,7 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14652,7 +15635,7 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14687,7 +15670,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14722,7 +15705,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14757,7 +15740,7 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14792,7 +15775,7 @@
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14811,12 +15794,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16545,12 +17528,12 @@
   <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20320,10 +21303,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20493,12 +21476,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20692,24 +21675,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20900,7 +21883,7 @@
         <v>0.3699436303194559</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1985206859207438</v>
+        <v>0.1985206859207439</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1511.392</v>
@@ -20912,7 +21895,7 @@
         <v>1811.434576535125</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1900.391475374193</v>
+        <v>1900.391475374194</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>1750</v>
@@ -20932,7 +21915,7 @@
         <v/>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>0.668106795393244</v>
+        <v>0.6681067953932439</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>0.0699336938382162</v>
@@ -21032,20 +22015,20 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21163,7 +22146,7 @@
         <v>0.0969582412221319</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.4707852330787171</v>
+        <v>0.470785233078717</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0.6861379111218948</v>
@@ -21246,9 +22229,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
